--- a/output/zone_monthly_4_01/renewable_electricity_generation_4_01.xlsx
+++ b/output/zone_monthly_4_01/renewable_electricity_generation_4_01.xlsx
@@ -3508,7 +3508,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4-01 使用；原始英文表頭為 Biogas</t>
+          <t>4-01 / 4-02 使用；原始英文表頭為 Biogas</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4-01 使用</t>
+          <t>4-01 / 4-02 使用</t>
         </is>
       </c>
     </row>

--- a/output/zone_monthly_4_01/renewable_electricity_generation_4_01.xlsx
+++ b/output/zone_monthly_4_01/renewable_electricity_generation_4_01.xlsx
@@ -3916,7 +3916,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>例如：全國、台電、民營電廠、自用發電設備、再生能源</t>
+          <t>例如：全國、台電、民營電廠、自用發電設備、再生能源、直轉供及躉售</t>
         </is>
       </c>
     </row>

--- a/output/zone_monthly_4_01/renewable_electricity_generation_4_01.xlsx
+++ b/output/zone_monthly_4_01/renewable_electricity_generation_4_01.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,67 +557,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3174732.305016</v>
+        <v>2997374.259236</v>
       </c>
       <c r="E2" t="n">
-        <v>196148.982</v>
+        <v>196554.206</v>
       </c>
       <c r="F2" t="n">
-        <v>6.178441618214215</v>
+        <v>6.557546338911299</v>
       </c>
       <c r="G2" t="n">
         <v>2692.654</v>
       </c>
       <c r="H2" t="n">
-        <v>0.084815151052127</v>
+        <v>0.089833760055253</v>
       </c>
       <c r="I2" t="n">
-        <v>890989.10137</v>
+        <v>949638.70571</v>
       </c>
       <c r="J2" t="n">
-        <v>28.06501511835372</v>
+        <v>31.68235340594581</v>
       </c>
       <c r="K2" t="n">
-        <v>1697965.3471</v>
+        <v>1461552.47298</v>
       </c>
       <c r="L2" t="n">
-        <v>53.4837329250487</v>
+        <v>48.76109376319707</v>
       </c>
       <c r="M2" t="n">
         <v>295424.6</v>
       </c>
       <c r="N2" t="n">
-        <v>9.305496388884073</v>
+        <v>9.856113199400754</v>
       </c>
       <c r="O2" t="n">
-        <v>1402540.7471</v>
+        <v>1166127.87298</v>
       </c>
       <c r="P2" t="n">
-        <v>44.17823653616462</v>
+        <v>38.90498056379632</v>
       </c>
       <c r="Q2" t="n">
         <v>19233.884856</v>
       </c>
       <c r="R2" t="n">
-        <v>0.605842729656637</v>
+        <v>0.641691133388946</v>
       </c>
       <c r="S2" t="n">
         <v>14391.803295</v>
       </c>
       <c r="T2" t="n">
-        <v>0.453323364375047</v>
+        <v>0.480147023704285</v>
       </c>
       <c r="U2" t="n">
         <v>4842.081561</v>
       </c>
       <c r="V2" t="n">
-        <v>0.15251936528159</v>
+        <v>0.161544109684661</v>
       </c>
       <c r="W2" t="n">
         <v>367702.33569</v>
       </c>
       <c r="X2" t="n">
-        <v>11.58215245767459</v>
+        <v>12.2674815985016</v>
       </c>
     </row>
     <row r="3">
@@ -637,67 +637,67 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3117824.818833</v>
+        <v>3174212.190773</v>
       </c>
       <c r="E3" t="n">
-        <v>312050.33</v>
+        <v>312491.291</v>
       </c>
       <c r="F3" t="n">
-        <v>10.00859086485816</v>
+        <v>9.844688137370571</v>
       </c>
       <c r="G3" t="n">
         <v>2260.769</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07251109768400001</v>
+        <v>0.071222995317444</v>
       </c>
       <c r="I3" t="n">
-        <v>968767.86574</v>
+        <v>1027481.38511</v>
       </c>
       <c r="J3" t="n">
-        <v>31.07191462099559</v>
+        <v>32.36965027406636</v>
       </c>
       <c r="K3" t="n">
-        <v>1497032.8806</v>
+        <v>1494265.77217</v>
       </c>
       <c r="L3" t="n">
-        <v>48.01529808722027</v>
+        <v>47.07516959684126</v>
       </c>
       <c r="M3" t="n">
-        <v>248884.85</v>
+        <v>248366.84232</v>
       </c>
       <c r="N3" t="n">
-        <v>7.982643812975915</v>
+        <v>7.824519200133137</v>
       </c>
       <c r="O3" t="n">
-        <v>1248148.0306</v>
+        <v>1245898.92985</v>
       </c>
       <c r="P3" t="n">
-        <v>40.03265427424435</v>
+        <v>39.25065039670812</v>
       </c>
       <c r="Q3" t="n">
         <v>23103.078114</v>
       </c>
       <c r="R3" t="n">
-        <v>0.740999878326951</v>
+        <v>0.727836600878715</v>
       </c>
       <c r="S3" t="n">
         <v>18161.899485</v>
       </c>
       <c r="T3" t="n">
-        <v>0.582518279259769</v>
+        <v>0.572170302218426</v>
       </c>
       <c r="U3" t="n">
         <v>4941.178629</v>
       </c>
       <c r="V3" t="n">
-        <v>0.158481599067182</v>
+        <v>0.155666298660289</v>
       </c>
       <c r="W3" t="n">
         <v>314609.895379</v>
       </c>
       <c r="X3" t="n">
-        <v>10.09068545091505</v>
+        <v>9.911432395525663</v>
       </c>
     </row>
     <row r="4">
@@ -717,67 +717,67 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3193868.753586</v>
+        <v>3543273.417106</v>
       </c>
       <c r="E4" t="n">
-        <v>389378.2</v>
+        <v>390208.861</v>
       </c>
       <c r="F4" t="n">
-        <v>12.19142770230666</v>
+        <v>11.01266583369416</v>
       </c>
       <c r="G4" t="n">
         <v>2512.292</v>
       </c>
       <c r="H4" t="n">
-        <v>0.078659838391269</v>
+        <v>0.07090313685281301</v>
       </c>
       <c r="I4" t="n">
-        <v>1199343.6277</v>
+        <v>1312982.09843</v>
       </c>
       <c r="J4" t="n">
-        <v>37.55143746446706</v>
+        <v>37.05562466873894</v>
       </c>
       <c r="K4" t="n">
-        <v>1261105.9991</v>
+        <v>1496041.53089</v>
       </c>
       <c r="L4" t="n">
-        <v>39.48521671981856</v>
+        <v>42.22201774403019</v>
       </c>
       <c r="M4" t="n">
-        <v>204044.713</v>
+        <v>203997.74311</v>
       </c>
       <c r="N4" t="n">
-        <v>6.388638004329497</v>
+        <v>5.757324346609893</v>
       </c>
       <c r="O4" t="n">
-        <v>1057061.2861</v>
+        <v>1292043.78778</v>
       </c>
       <c r="P4" t="n">
-        <v>33.09657871548907</v>
+        <v>36.46469339742029</v>
       </c>
       <c r="Q4" t="n">
         <v>24704.981935</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7735127471115349</v>
+        <v>0.6972361155007341</v>
       </c>
       <c r="S4" t="n">
         <v>19508.038966</v>
       </c>
       <c r="T4" t="n">
-        <v>0.610796512664988</v>
+        <v>0.550565442447096</v>
       </c>
       <c r="U4" t="n">
         <v>5196.942969</v>
       </c>
       <c r="V4" t="n">
-        <v>0.162716234446547</v>
+        <v>0.146670673053638</v>
       </c>
       <c r="W4" t="n">
         <v>316823.652851</v>
       </c>
       <c r="X4" t="n">
-        <v>9.919745527904926</v>
+        <v>8.941552501183175</v>
       </c>
     </row>
     <row r="5">
@@ -797,67 +797,67 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2830536.441526</v>
+        <v>2949070.718186</v>
       </c>
       <c r="E5" t="n">
-        <v>454415.151</v>
+        <v>455226.996</v>
       </c>
       <c r="F5" t="n">
-        <v>16.05402934699599</v>
+        <v>15.43628618984133</v>
       </c>
       <c r="G5" t="n">
         <v>2372.472</v>
       </c>
       <c r="H5" t="n">
-        <v>0.083817044896301</v>
+        <v>0.08044812168693399</v>
       </c>
       <c r="I5" t="n">
-        <v>1348084.24067</v>
+        <v>1465893.87404</v>
       </c>
       <c r="J5" t="n">
-        <v>47.62645768811301</v>
+        <v>49.70697599756728</v>
       </c>
       <c r="K5" t="n">
-        <v>716609.6868</v>
+        <v>716522.48509</v>
       </c>
       <c r="L5" t="n">
-        <v>25.3170980697094</v>
+        <v>24.29655147539966</v>
       </c>
       <c r="M5" t="n">
-        <v>93080.755</v>
+        <v>93671.70163</v>
       </c>
       <c r="N5" t="n">
-        <v>3.28844927182136</v>
+        <v>3.176312492350754</v>
       </c>
       <c r="O5" t="n">
-        <v>623528.9318</v>
+        <v>622850.7834599999</v>
       </c>
       <c r="P5" t="n">
-        <v>22.02864879788804</v>
+        <v>21.12023898304891</v>
       </c>
       <c r="Q5" t="n">
         <v>21545.239307</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7611715924556171</v>
+        <v>0.730577234860365</v>
       </c>
       <c r="S5" t="n">
         <v>16358.587387</v>
       </c>
       <c r="T5" t="n">
-        <v>0.57793240698151</v>
+        <v>0.554703123466036</v>
       </c>
       <c r="U5" t="n">
         <v>5186.65192</v>
       </c>
       <c r="V5" t="n">
-        <v>0.183239185474106</v>
+        <v>0.17587411139433</v>
       </c>
       <c r="W5" t="n">
         <v>287509.651749</v>
       </c>
       <c r="X5" t="n">
-        <v>10.15742625782969</v>
+        <v>9.749160980644431</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3141803.355137</v>
+        <v>3193203.903177</v>
       </c>
       <c r="E6" t="n">
-        <v>620063.075</v>
+        <v>619932.862</v>
       </c>
       <c r="F6" t="n">
-        <v>19.73589702825184</v>
+        <v>19.41413329049275</v>
       </c>
       <c r="G6" t="n">
         <v>2134.444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06793690625194899</v>
+        <v>0.066843335556379</v>
       </c>
       <c r="I6" t="n">
-        <v>1555363.38309</v>
+        <v>1608643.32359</v>
       </c>
       <c r="J6" t="n">
-        <v>49.50543389505602</v>
+        <v>50.37709373928548</v>
       </c>
       <c r="K6" t="n">
-        <v>609573.4845</v>
+        <v>607824.30504</v>
       </c>
       <c r="L6" t="n">
-        <v>19.40202538466699</v>
+        <v>19.03493555282392</v>
       </c>
       <c r="M6" t="n">
-        <v>68516.19899999999</v>
+        <v>68512.46802</v>
       </c>
       <c r="N6" t="n">
-        <v>2.180792088339097</v>
+        <v>2.145571347693619</v>
       </c>
       <c r="O6" t="n">
-        <v>541057.2855</v>
+        <v>539311.83702</v>
       </c>
       <c r="P6" t="n">
-        <v>17.22123329632789</v>
+        <v>16.8893642051303</v>
       </c>
       <c r="Q6" t="n">
         <v>23469.241859</v>
       </c>
       <c r="R6" t="n">
-        <v>0.74699907047418</v>
+        <v>0.734974732921059</v>
       </c>
       <c r="S6" t="n">
         <v>18435.974287</v>
       </c>
       <c r="T6" t="n">
-        <v>0.586795932242427</v>
+        <v>0.577350361768554</v>
       </c>
       <c r="U6" t="n">
         <v>5033.267572</v>
       </c>
       <c r="V6" t="n">
-        <v>0.160203138231754</v>
+        <v>0.157624371152505</v>
       </c>
       <c r="W6" t="n">
         <v>331199.726688</v>
       </c>
       <c r="X6" t="n">
-        <v>10.541707715299</v>
+        <v>10.3720193489204</v>
       </c>
     </row>
     <row r="7">
@@ -957,67 +957,67 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3002932.354883</v>
+        <v>3074959.835927</v>
       </c>
       <c r="E7" t="n">
-        <v>602426.3590000001</v>
+        <v>607311.713</v>
       </c>
       <c r="F7" t="n">
-        <v>20.06126971259969</v>
+        <v>19.75023237391051</v>
       </c>
       <c r="G7" t="n">
         <v>2469.788</v>
       </c>
       <c r="H7" t="n">
-        <v>0.082245875301984</v>
+        <v>0.08031935803335299</v>
       </c>
       <c r="I7" t="n">
-        <v>1629736.44722</v>
+        <v>1688741.05057</v>
       </c>
       <c r="J7" t="n">
-        <v>54.27150047419227</v>
+        <v>54.91912547406981</v>
       </c>
       <c r="K7" t="n">
-        <v>438704.2255</v>
+        <v>438663.01303</v>
       </c>
       <c r="L7" t="n">
-        <v>14.60919440248572</v>
+        <v>14.26565016898041</v>
       </c>
       <c r="M7" t="n">
-        <v>58426.147</v>
+        <v>58447.82196</v>
       </c>
       <c r="N7" t="n">
-        <v>1.945636467801034</v>
+        <v>1.900767004404787</v>
       </c>
       <c r="O7" t="n">
-        <v>380278.0785</v>
+        <v>380215.19107</v>
       </c>
       <c r="P7" t="n">
-        <v>12.66355793468469</v>
+        <v>12.36488316457563</v>
       </c>
       <c r="Q7" t="n">
-        <v>21761.918733</v>
+        <v>21390.172139</v>
       </c>
       <c r="R7" t="n">
-        <v>0.724688942713393</v>
+        <v>0.695624440003509</v>
       </c>
       <c r="S7" t="n">
-        <v>17145.037533</v>
+        <v>16773.290939</v>
       </c>
       <c r="T7" t="n">
-        <v>0.570943181757686</v>
+        <v>0.545480000845065</v>
       </c>
       <c r="U7" t="n">
         <v>4616.8812</v>
       </c>
       <c r="V7" t="n">
-        <v>0.153745760955707</v>
+        <v>0.150144439158444</v>
       </c>
       <c r="W7" t="n">
-        <v>307833.61643</v>
+        <v>316384.099188</v>
       </c>
       <c r="X7" t="n">
-        <v>10.25110059270695</v>
+        <v>10.28904818500241</v>
       </c>
     </row>
     <row r="8">
@@ -1037,67 +1037,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3157224.804267</v>
+        <v>3252354.531255</v>
       </c>
       <c r="E8" t="n">
-        <v>667588.083</v>
+        <v>667565.031</v>
       </c>
       <c r="F8" t="n">
-        <v>21.14477505997522</v>
+        <v>20.52559229274442</v>
       </c>
       <c r="G8" t="n">
         <v>1376.108</v>
       </c>
       <c r="H8" t="n">
-        <v>0.043585999899031</v>
+        <v>0.042311131421118</v>
       </c>
       <c r="I8" t="n">
-        <v>1442960.33119</v>
+        <v>1537636.56391</v>
       </c>
       <c r="J8" t="n">
-        <v>45.70343959162598</v>
+        <v>47.27764298551627</v>
       </c>
       <c r="K8" t="n">
-        <v>693346.1973</v>
+        <v>691777.0165499999</v>
       </c>
       <c r="L8" t="n">
-        <v>21.96062175753023</v>
+        <v>21.27003713469887</v>
       </c>
       <c r="M8" t="n">
-        <v>87259.508</v>
+        <v>87251.51424999999</v>
       </c>
       <c r="N8" t="n">
-        <v>2.763804081422029</v>
+        <v>2.682718424806286</v>
       </c>
       <c r="O8" t="n">
-        <v>606086.6893</v>
+        <v>604525.5023000001</v>
       </c>
       <c r="P8" t="n">
-        <v>19.1968176761082</v>
+        <v>18.58731870989258</v>
       </c>
       <c r="Q8" t="n">
-        <v>24134.05617</v>
+        <v>27140.25871</v>
       </c>
       <c r="R8" t="n">
-        <v>0.764407277473012</v>
+        <v>0.83448032645836</v>
       </c>
       <c r="S8" t="n">
-        <v>18686.263962</v>
+        <v>21692.466502</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5918572518734</v>
+        <v>0.666977301937296</v>
       </c>
       <c r="U8" t="n">
         <v>5447.792208</v>
       </c>
       <c r="V8" t="n">
-        <v>0.172550025599612</v>
+        <v>0.167503024521064</v>
       </c>
       <c r="W8" t="n">
-        <v>327820.028607</v>
+        <v>326859.553085</v>
       </c>
       <c r="X8" t="n">
-        <v>10.38317031349653</v>
+        <v>10.04993612916096</v>
       </c>
     </row>
     <row r="9">
@@ -1117,67 +1117,67 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3055253.651368</v>
+        <v>3079335.041924</v>
       </c>
       <c r="E9" t="n">
-        <v>748442.823</v>
+        <v>748382.878</v>
       </c>
       <c r="F9" t="n">
-        <v>24.49691280672824</v>
+        <v>24.30339238215542</v>
       </c>
       <c r="G9" t="n">
         <v>2299.591</v>
       </c>
       <c r="H9" t="n">
-        <v>0.075266778552751</v>
+        <v>0.074678168133442</v>
       </c>
       <c r="I9" t="n">
-        <v>1552330.5237</v>
+        <v>1576000.79608</v>
       </c>
       <c r="J9" t="n">
-        <v>50.80856455256796</v>
+        <v>51.17990652603033</v>
       </c>
       <c r="K9" t="n">
-        <v>387513.9666</v>
+        <v>387914.12839</v>
       </c>
       <c r="L9" t="n">
-        <v>12.68352846666231</v>
+        <v>12.59733426563507</v>
       </c>
       <c r="M9" t="n">
-        <v>53500.09</v>
+        <v>53504.67033</v>
       </c>
       <c r="N9" t="n">
-        <v>1.751085052334204</v>
+        <v>1.737539748080473</v>
       </c>
       <c r="O9" t="n">
-        <v>334013.8766</v>
+        <v>334409.45806</v>
       </c>
       <c r="P9" t="n">
-        <v>10.93244341432811</v>
+        <v>10.85979451755459</v>
       </c>
       <c r="Q9" t="n">
-        <v>16764.012138</v>
+        <v>16761.473973</v>
       </c>
       <c r="R9" t="n">
-        <v>0.548694611018429</v>
+        <v>0.544321216912053</v>
       </c>
       <c r="S9" t="n">
-        <v>10436.171917</v>
+        <v>10433.633752</v>
       </c>
       <c r="T9" t="n">
-        <v>0.34158119448862</v>
+        <v>0.338827493921576</v>
       </c>
       <c r="U9" t="n">
         <v>6327.840221</v>
       </c>
       <c r="V9" t="n">
-        <v>0.207113416529809</v>
+        <v>0.205493722990477</v>
       </c>
       <c r="W9" t="n">
-        <v>347902.73493</v>
+        <v>347976.174481</v>
       </c>
       <c r="X9" t="n">
-        <v>11.3870327844703</v>
+        <v>11.30036744113368</v>
       </c>
     </row>
     <row r="10">
@@ -1197,67 +1197,67 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2597075.956402</v>
+        <v>2639858.856839</v>
       </c>
       <c r="E10" t="n">
-        <v>527552.581</v>
+        <v>527486.112</v>
       </c>
       <c r="F10" t="n">
-        <v>20.31332890744072</v>
+        <v>19.9816028282519</v>
       </c>
       <c r="G10" t="n">
         <v>2246.823</v>
       </c>
       <c r="H10" t="n">
-        <v>0.086513565167834</v>
+        <v>0.085111482160466</v>
       </c>
       <c r="I10" t="n">
-        <v>1555454.62002</v>
+        <v>1598476.03555</v>
       </c>
       <c r="J10" t="n">
-        <v>59.89253476340112</v>
+        <v>60.55157196790571</v>
       </c>
       <c r="K10" t="n">
-        <v>160721.9951</v>
+        <v>159719.17875</v>
       </c>
       <c r="L10" t="n">
-        <v>6.188575066655537</v>
+        <v>6.050292360753322</v>
       </c>
       <c r="M10" t="n">
-        <v>25407.567</v>
+        <v>25438.64293</v>
       </c>
       <c r="N10" t="n">
-        <v>0.978314359168753</v>
+        <v>0.963636478673733</v>
       </c>
       <c r="O10" t="n">
-        <v>135314.4281</v>
+        <v>134280.53582</v>
       </c>
       <c r="P10" t="n">
-        <v>5.210260707486784</v>
+        <v>5.086655882079589</v>
       </c>
       <c r="Q10" t="n">
-        <v>23340.597454</v>
+        <v>24662.017269</v>
       </c>
       <c r="R10" t="n">
-        <v>0.898726022874439</v>
+        <v>0.934217267150813</v>
       </c>
       <c r="S10" t="n">
-        <v>17261.045373</v>
+        <v>18580.084586</v>
       </c>
       <c r="T10" t="n">
-        <v>0.664633829074199</v>
+        <v>0.703828711821663</v>
       </c>
       <c r="U10" t="n">
-        <v>6079.552081</v>
+        <v>6081.932683</v>
       </c>
       <c r="V10" t="n">
-        <v>0.23409219380024</v>
+        <v>0.230388555329151</v>
       </c>
       <c r="W10" t="n">
-        <v>327759.339828</v>
+        <v>327268.69027</v>
       </c>
       <c r="X10" t="n">
-        <v>12.62032167446035</v>
+        <v>12.39720409377779</v>
       </c>
     </row>
     <row r="11">
@@ -1277,67 +1277,67 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3243138.391733</v>
+        <v>3289105.087055</v>
       </c>
       <c r="E11" t="n">
-        <v>428804.731</v>
+        <v>428763.653</v>
       </c>
       <c r="F11" t="n">
-        <v>13.22190665970515</v>
+        <v>13.03587576716518</v>
       </c>
       <c r="G11" t="n">
         <v>2018.42</v>
       </c>
       <c r="H11" t="n">
-        <v>0.062236628728059</v>
+        <v>0.061366844371861</v>
       </c>
       <c r="I11" t="n">
-        <v>1495119.31194</v>
+        <v>1538399.79678</v>
       </c>
       <c r="J11" t="n">
-        <v>46.10100252740278</v>
+        <v>46.77259485671992</v>
       </c>
       <c r="K11" t="n">
-        <v>980406.6419</v>
+        <v>983136.37369</v>
       </c>
       <c r="L11" t="n">
-        <v>30.23018210999349</v>
+        <v>29.89069511823598</v>
       </c>
       <c r="M11" t="n">
-        <v>172067.746</v>
+        <v>172052.11248</v>
       </c>
       <c r="N11" t="n">
-        <v>5.305593694016062</v>
+        <v>5.230970368114693</v>
       </c>
       <c r="O11" t="n">
-        <v>808338.8959</v>
+        <v>811084.26121</v>
       </c>
       <c r="P11" t="n">
-        <v>24.92458841597743</v>
+        <v>24.65972475012128</v>
       </c>
       <c r="Q11" t="n">
-        <v>25305.643114</v>
+        <v>25305.480999</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7802825552713371</v>
+        <v>0.769372833315521</v>
       </c>
       <c r="S11" t="n">
-        <v>18804.827908</v>
+        <v>18804.477836</v>
       </c>
       <c r="T11" t="n">
-        <v>0.579834272750583</v>
+        <v>0.571720189482823</v>
       </c>
       <c r="U11" t="n">
-        <v>6500.815206</v>
+        <v>6501.003163</v>
       </c>
       <c r="V11" t="n">
-        <v>0.200448282520754</v>
+        <v>0.197652643832699</v>
       </c>
       <c r="W11" t="n">
-        <v>311483.643779</v>
+        <v>311481.362586</v>
       </c>
       <c r="X11" t="n">
-        <v>9.60438951889919</v>
+        <v>9.470094580191548</v>
       </c>
     </row>
     <row r="12">
@@ -1357,67 +1357,67 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3710725.935695</v>
+        <v>3759746.249389</v>
       </c>
       <c r="E12" t="n">
-        <v>367573.62</v>
+        <v>367526.4</v>
       </c>
       <c r="F12" t="n">
-        <v>9.905706494358906</v>
+        <v>9.775298002085304</v>
       </c>
       <c r="G12" t="n">
         <v>1498.411</v>
       </c>
       <c r="H12" t="n">
-        <v>0.040380535398375</v>
+        <v>0.039854046007587</v>
       </c>
       <c r="I12" t="n">
-        <v>1215068.62263</v>
+        <v>1264408.16597</v>
       </c>
       <c r="J12" t="n">
-        <v>32.74476864329307</v>
+        <v>33.63014634765525</v>
       </c>
       <c r="K12" t="n">
-        <v>1833861.0477</v>
+        <v>1833587.8612</v>
       </c>
       <c r="L12" t="n">
-        <v>49.42054680081155</v>
+        <v>48.76892586828109</v>
       </c>
       <c r="M12" t="n">
-        <v>314127.712</v>
+        <v>314071.47299</v>
       </c>
       <c r="N12" t="n">
-        <v>8.465397807428358</v>
+        <v>8.353528460625236</v>
       </c>
       <c r="O12" t="n">
-        <v>1519733.3357</v>
+        <v>1519516.38821</v>
       </c>
       <c r="P12" t="n">
-        <v>40.95514899338319</v>
+        <v>40.41539740765586</v>
       </c>
       <c r="Q12" t="n">
-        <v>21978.321968</v>
+        <v>21979.498822</v>
       </c>
       <c r="R12" t="n">
-        <v>0.592291706498221</v>
+        <v>0.5846005917439751</v>
       </c>
       <c r="S12" t="n">
         <v>17902.162957</v>
       </c>
       <c r="T12" t="n">
-        <v>0.482443685339079</v>
+        <v>0.476153489345439</v>
       </c>
       <c r="U12" t="n">
-        <v>4076.159011</v>
+        <v>4077.335865</v>
       </c>
       <c r="V12" t="n">
-        <v>0.109848021159142</v>
+        <v>0.108447102398536</v>
       </c>
       <c r="W12" t="n">
         <v>270745.912397</v>
       </c>
       <c r="X12" t="n">
-        <v>7.296305819639862</v>
+        <v>7.2011751442268</v>
       </c>
     </row>
     <row r="13">
@@ -1437,67 +1437,67 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3588619.108312</v>
+        <v>3644748.786457</v>
       </c>
       <c r="E13" t="n">
-        <v>184713.49</v>
+        <v>184698.833</v>
       </c>
       <c r="F13" t="n">
-        <v>5.147202431491394</v>
+        <v>5.067532601596465</v>
       </c>
       <c r="G13" t="n">
         <v>1961.026</v>
       </c>
       <c r="H13" t="n">
-        <v>0.054645699106318</v>
+        <v>0.053804147141408</v>
       </c>
       <c r="I13" t="n">
-        <v>1121888.86585</v>
+        <v>1170850.87014</v>
       </c>
       <c r="J13" t="n">
-        <v>31.2624113061057</v>
+        <v>32.12432292976123</v>
       </c>
       <c r="K13" t="n">
-        <v>1925609.4277</v>
+        <v>1932283.57213</v>
       </c>
       <c r="L13" t="n">
-        <v>53.65878544312161</v>
+        <v>53.01554881669475</v>
       </c>
       <c r="M13" t="n">
         <v>293827.265</v>
       </c>
       <c r="N13" t="n">
-        <v>8.187752896913302</v>
+        <v>8.061660273865531</v>
       </c>
       <c r="O13" t="n">
-        <v>1631782.1627</v>
+        <v>1638456.30713</v>
       </c>
       <c r="P13" t="n">
-        <v>45.47103254620831</v>
+        <v>44.95388854282921</v>
       </c>
       <c r="Q13" t="n">
-        <v>23957.828138</v>
+        <v>23787.486086</v>
       </c>
       <c r="R13" t="n">
-        <v>0.667605767424818</v>
+        <v>0.652650909011576</v>
       </c>
       <c r="S13" t="n">
-        <v>19498.58954</v>
+        <v>19328.102959</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5433451963413209</v>
+        <v>0.530300003962373</v>
       </c>
       <c r="U13" t="n">
-        <v>4459.238598</v>
+        <v>4459.383127</v>
       </c>
       <c r="V13" t="n">
-        <v>0.124260571083497</v>
+        <v>0.122350905049203</v>
       </c>
       <c r="W13" t="n">
-        <v>330488.470624</v>
+        <v>331166.999101</v>
       </c>
       <c r="X13" t="n">
-        <v>9.209349352750166</v>
+        <v>9.086140595794586</v>
       </c>
     </row>
     <row r="14">
@@ -1517,67 +1517,67 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3578490.736052</v>
+        <v>3583484.224949</v>
       </c>
       <c r="E14" t="n">
-        <v>222806.588</v>
+        <v>222792.848</v>
       </c>
       <c r="F14" t="n">
-        <v>6.226272594624997</v>
+        <v>6.21721302549255</v>
       </c>
       <c r="G14" t="n">
         <v>2111.674</v>
       </c>
       <c r="H14" t="n">
-        <v>0.059010184900736</v>
+        <v>0.058927955795035</v>
       </c>
       <c r="I14" t="n">
-        <v>1101412.19193</v>
+        <v>1101730.63593</v>
       </c>
       <c r="J14" t="n">
-        <v>30.77867942576099</v>
+        <v>30.74467659881158</v>
       </c>
       <c r="K14" t="n">
         <v>1887698.712</v>
       </c>
       <c r="L14" t="n">
-        <v>52.75125328625607</v>
+        <v>52.67774583343856</v>
       </c>
       <c r="M14" t="n">
         <v>314876.521</v>
       </c>
       <c r="N14" t="n">
-        <v>8.799143108789773</v>
+        <v>8.786881739502601</v>
       </c>
       <c r="O14" t="n">
         <v>1572822.191</v>
       </c>
       <c r="P14" t="n">
-        <v>43.9521101774663</v>
+        <v>43.89086409393596</v>
       </c>
       <c r="Q14" t="n">
-        <v>25320.527467</v>
+        <v>23890.160716</v>
       </c>
       <c r="R14" t="n">
-        <v>0.70757560476278</v>
+        <v>0.666674086345113</v>
       </c>
       <c r="S14" t="n">
-        <v>20887.366441</v>
+        <v>19456.99969</v>
       </c>
       <c r="T14" t="n">
-        <v>0.583692064103096</v>
+        <v>0.542963174067744</v>
       </c>
       <c r="U14" t="n">
         <v>4433.161026</v>
       </c>
       <c r="V14" t="n">
-        <v>0.123883540659684</v>
+        <v>0.123710912277369</v>
       </c>
       <c r="W14" t="n">
-        <v>339141.042655</v>
+        <v>345260.194303</v>
       </c>
       <c r="X14" t="n">
-        <v>9.477208903694416</v>
+        <v>9.634762500117152</v>
       </c>
     </row>
     <row r="15">
@@ -1597,67 +1597,67 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2891923.665627</v>
+        <v>2900985.123137</v>
       </c>
       <c r="E15" t="n">
-        <v>230652.122</v>
+        <v>230624.778</v>
       </c>
       <c r="F15" t="n">
-        <v>7.97573341030743</v>
+        <v>7.94987799698236</v>
       </c>
       <c r="G15" t="n">
         <v>1704.3</v>
       </c>
       <c r="H15" t="n">
-        <v>0.058933090809314</v>
+        <v>0.058749008618046</v>
       </c>
       <c r="I15" t="n">
-        <v>1146571.70406</v>
+        <v>1155660.50557</v>
       </c>
       <c r="J15" t="n">
-        <v>39.64737097621181</v>
+        <v>39.83682978423269</v>
       </c>
       <c r="K15" t="n">
         <v>1155732.9213</v>
       </c>
       <c r="L15" t="n">
-        <v>39.96415725065222</v>
+        <v>39.83932603040171</v>
       </c>
       <c r="M15" t="n">
         <v>191202.992</v>
       </c>
       <c r="N15" t="n">
-        <v>6.611619603678063</v>
+        <v>6.590967684565075</v>
       </c>
       <c r="O15" t="n">
         <v>964529.9293</v>
       </c>
       <c r="P15" t="n">
-        <v>33.35253764697415</v>
+        <v>33.24835834583664</v>
       </c>
       <c r="Q15" t="n">
         <v>24076.53597</v>
       </c>
       <c r="R15" t="n">
-        <v>0.832543965671374</v>
+        <v>0.829943448450528</v>
       </c>
       <c r="S15" t="n">
         <v>20394.679405</v>
       </c>
       <c r="T15" t="n">
-        <v>0.70522882908039</v>
+        <v>0.703025990803637</v>
       </c>
       <c r="U15" t="n">
         <v>3681.856565</v>
       </c>
       <c r="V15" t="n">
-        <v>0.127315136590984</v>
+        <v>0.126917457646891</v>
       </c>
       <c r="W15" t="n">
         <v>333186.082297</v>
       </c>
       <c r="X15" t="n">
-        <v>11.52126130634785</v>
+        <v>11.48527373131466</v>
       </c>
     </row>
     <row r="16">
@@ -1677,67 +1677,147 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3449730.827776</v>
+        <v>3457180.938606</v>
       </c>
       <c r="E16" t="n">
         <v>243613.974</v>
       </c>
       <c r="F16" t="n">
-        <v>7.061825578926545</v>
+        <v>7.046607577855895</v>
       </c>
       <c r="G16" t="n">
         <v>2212.953</v>
       </c>
       <c r="H16" t="n">
-        <v>0.064148570148781</v>
+        <v>0.064010332097119</v>
       </c>
       <c r="I16" t="n">
-        <v>1521815.61748</v>
+        <v>1529265.72831</v>
       </c>
       <c r="J16" t="n">
-        <v>44.11403942669627</v>
+        <v>44.23447182740249</v>
       </c>
       <c r="K16" t="n">
         <v>1335293.307</v>
       </c>
       <c r="L16" t="n">
-        <v>38.7071737959581</v>
+        <v>38.62376111382864</v>
       </c>
       <c r="M16" t="n">
         <v>208868.447</v>
       </c>
       <c r="N16" t="n">
-        <v>6.054630271969797</v>
+        <v>6.041582743546528</v>
       </c>
       <c r="O16" t="n">
         <v>1126424.86</v>
       </c>
       <c r="P16" t="n">
-        <v>32.6525435239883</v>
+        <v>32.58217837028211</v>
       </c>
       <c r="Q16" t="n">
         <v>28368.082229</v>
       </c>
       <c r="R16" t="n">
-        <v>0.822327411767618</v>
+        <v>0.820555323333425</v>
       </c>
       <c r="S16" t="n">
         <v>23679.884107</v>
       </c>
       <c r="T16" t="n">
-        <v>0.686427008053441</v>
+        <v>0.684947780504314</v>
       </c>
       <c r="U16" t="n">
         <v>4688.198122</v>
       </c>
       <c r="V16" t="n">
-        <v>0.135900403714177</v>
+        <v>0.135607542829111</v>
       </c>
       <c r="W16" t="n">
         <v>318426.894067</v>
       </c>
       <c r="X16" t="n">
-        <v>9.230485216502704</v>
+        <v>9.210593825482437</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>04月</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2797695.567477</v>
+      </c>
+      <c r="E17" t="n">
+        <v>209017.05</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7.471043398352824</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2526.753</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.090315509284617</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1489256.29348</v>
+      </c>
+      <c r="J17" t="n">
+        <v>53.2315349387007</v>
+      </c>
+      <c r="K17" t="n">
+        <v>785479.302</v>
+      </c>
+      <c r="L17" t="n">
+        <v>28.07593903822623</v>
+      </c>
+      <c r="M17" t="n">
+        <v>92298.88499999999</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.299103950871838</v>
+      </c>
+      <c r="O17" t="n">
+        <v>693180.417</v>
+      </c>
+      <c r="P17" t="n">
+        <v>24.7768350873544</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>24845.848804</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.888082645332506</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20899.890298</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.747039475665603</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3945.958506</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.141043169666903</v>
+      </c>
+      <c r="W17" t="n">
+        <v>286570.320193</v>
+      </c>
+      <c r="X17" t="n">
+        <v>10.24308447010312</v>
       </c>
     </row>
   </sheetData>
@@ -3093,67 +3173,67 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>24106371.67641</v>
+        <v>24110836.364907</v>
       </c>
       <c r="E17" t="n">
         <v>5836502.66401</v>
       </c>
       <c r="F17" t="n">
-        <v>24.21145223493539</v>
+        <v>24.20696891504333</v>
       </c>
       <c r="G17" t="n">
         <v>25007.71</v>
       </c>
       <c r="H17" t="n">
-        <v>0.103739004507559</v>
+        <v>0.103719794790688</v>
       </c>
       <c r="I17" t="n">
-        <v>10897964.43192</v>
+        <v>10898818.42392</v>
       </c>
       <c r="J17" t="n">
-        <v>45.20781716223402</v>
+        <v>45.20298781415598</v>
       </c>
       <c r="K17" t="n">
         <v>3577472.27299</v>
       </c>
       <c r="L17" t="n">
-        <v>14.84035972319651</v>
+        <v>14.83761168151331</v>
       </c>
       <c r="M17" t="n">
         <v>2082793.93799</v>
       </c>
       <c r="N17" t="n">
-        <v>8.640014208476588</v>
+        <v>8.638414306612271</v>
       </c>
       <c r="O17" t="n">
         <v>1494678.335</v>
       </c>
       <c r="P17" t="n">
-        <v>6.200345514719917</v>
+        <v>6.199197374901039</v>
       </c>
       <c r="Q17" t="n">
-        <v>164296.276394</v>
+        <v>164213.814059</v>
       </c>
       <c r="R17" t="n">
-        <v>0.681547097171728</v>
+        <v>0.681078879113505</v>
       </c>
       <c r="S17" t="n">
-        <v>118278.472608</v>
+        <v>118196.010273</v>
       </c>
       <c r="T17" t="n">
-        <v>0.490652322944746</v>
+        <v>0.490219453544269</v>
       </c>
       <c r="U17" t="n">
         <v>46017.803786</v>
       </c>
       <c r="V17" t="n">
-        <v>0.190894774226982</v>
+        <v>0.190859425569236</v>
       </c>
       <c r="W17" t="n">
-        <v>3605128.321096</v>
+        <v>3608821.479928</v>
       </c>
       <c r="X17" t="n">
-        <v>14.9550847779548</v>
+        <v>14.96763291538319</v>
       </c>
     </row>
     <row r="18">
@@ -3173,67 +3253,67 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27387278.884389</v>
+        <v>27432092.099754</v>
       </c>
       <c r="E18" t="n">
-        <v>3963022.166</v>
+        <v>3963919.556</v>
       </c>
       <c r="F18" t="n">
-        <v>14.47030273700889</v>
+        <v>14.44993528596219</v>
       </c>
       <c r="G18" t="n">
         <v>23164.354</v>
       </c>
       <c r="H18" t="n">
-        <v>0.084580706603911</v>
+        <v>0.084442535100003</v>
       </c>
       <c r="I18" t="n">
-        <v>13301584.9974</v>
+        <v>13340351.2854</v>
       </c>
       <c r="J18" t="n">
-        <v>48.56847974401</v>
+        <v>48.63045529626095</v>
       </c>
       <c r="K18" t="n">
         <v>6238286.52899</v>
       </c>
       <c r="L18" t="n">
-        <v>22.77804434432469</v>
+        <v>22.74083400677247</v>
       </c>
       <c r="M18" t="n">
         <v>1741013.43299</v>
       </c>
       <c r="N18" t="n">
-        <v>6.357015022702359</v>
+        <v>6.346630168267818</v>
       </c>
       <c r="O18" t="n">
         <v>4497273.096</v>
       </c>
       <c r="P18" t="n">
-        <v>16.42102932162233</v>
+        <v>16.39420383850465</v>
       </c>
       <c r="Q18" t="n">
-        <v>244180.950589</v>
+        <v>244040.018872</v>
       </c>
       <c r="R18" t="n">
-        <v>0.891585292645431</v>
+        <v>0.889615046437484</v>
       </c>
       <c r="S18" t="n">
-        <v>171338.484453</v>
+        <v>171197.552736</v>
       </c>
       <c r="T18" t="n">
-        <v>0.625613392174805</v>
+        <v>0.62407763911501</v>
       </c>
       <c r="U18" t="n">
         <v>72842.466136</v>
       </c>
       <c r="V18" t="n">
-        <v>0.265971900470626</v>
+        <v>0.265537407322474</v>
       </c>
       <c r="W18" t="n">
-        <v>3617039.88741</v>
+        <v>3622330.356492</v>
       </c>
       <c r="X18" t="n">
-        <v>13.20700717540707</v>
+        <v>13.20471782946691</v>
       </c>
     </row>
     <row r="19">
@@ -3253,67 +3333,67 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>33843284.12612</v>
+        <v>34129160.722314</v>
       </c>
       <c r="E19" t="n">
-        <v>4208168.16799</v>
+        <v>4210637.67799</v>
       </c>
       <c r="F19" t="n">
-        <v>12.43427840013365</v>
+        <v>12.33736074628123</v>
       </c>
       <c r="G19" t="n">
         <v>26740.734</v>
       </c>
       <c r="H19" t="n">
-        <v>0.079013413415637</v>
+        <v>0.078351572186528</v>
       </c>
       <c r="I19" t="n">
-        <v>15222589.79009</v>
+        <v>15498625.38828</v>
       </c>
       <c r="J19" t="n">
-        <v>44.979647168288</v>
+        <v>45.41168039373098</v>
       </c>
       <c r="K19" t="n">
         <v>10509811.45099</v>
       </c>
       <c r="L19" t="n">
-        <v>31.05434866138953</v>
+        <v>30.79422765916004</v>
       </c>
       <c r="M19" t="n">
         <v>1898368.85098</v>
       </c>
       <c r="N19" t="n">
-        <v>5.609292655835527</v>
+        <v>5.562307454395814</v>
       </c>
       <c r="O19" t="n">
         <v>8611442.60001</v>
       </c>
       <c r="P19" t="n">
-        <v>25.445056005554</v>
+        <v>25.23192020476422</v>
       </c>
       <c r="Q19" t="n">
-        <v>237716.122122</v>
+        <v>237409.188782</v>
       </c>
       <c r="R19" t="n">
-        <v>0.702402642829017</v>
+        <v>0.695619768425127</v>
       </c>
       <c r="S19" t="n">
-        <v>173769.79639</v>
+        <v>173462.86305</v>
       </c>
       <c r="T19" t="n">
-        <v>0.513454296404662</v>
+        <v>0.5082541128431211</v>
       </c>
       <c r="U19" t="n">
         <v>63946.325732</v>
       </c>
       <c r="V19" t="n">
-        <v>0.188948346424355</v>
+        <v>0.187365655582006</v>
       </c>
       <c r="W19" t="n">
-        <v>3638257.860928</v>
+        <v>3645936.282272</v>
       </c>
       <c r="X19" t="n">
-        <v>10.75030971394416</v>
+        <v>10.6827598602161</v>
       </c>
     </row>
     <row r="20">
@@ -3333,67 +3413,67 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>37813735.876758</v>
+        <v>38597242.877324</v>
       </c>
       <c r="E20" t="n">
-        <v>5499157.425</v>
+        <v>5506148.836</v>
       </c>
       <c r="F20" t="n">
-        <v>14.54275092765966</v>
+        <v>14.26565325792967</v>
       </c>
       <c r="G20" t="n">
         <v>25842.798</v>
       </c>
       <c r="H20" t="n">
-        <v>0.068342356026991</v>
+        <v>0.06695503635360101</v>
       </c>
       <c r="I20" t="n">
-        <v>15975106.94112</v>
+        <v>16739152.66588</v>
       </c>
       <c r="J20" t="n">
-        <v>42.24683589367061</v>
+        <v>43.36877822875349</v>
       </c>
       <c r="K20" t="n">
-        <v>12202450.8999</v>
+        <v>12203287.70991</v>
       </c>
       <c r="L20" t="n">
-        <v>32.26988980848139</v>
+        <v>31.61699333990374</v>
       </c>
       <c r="M20" t="n">
-        <v>1914567.152</v>
+        <v>1914566.85502</v>
       </c>
       <c r="N20" t="n">
-        <v>5.063152602112444</v>
+        <v>4.960372068816382</v>
       </c>
       <c r="O20" t="n">
-        <v>10287883.7479</v>
+        <v>10288720.85489</v>
       </c>
       <c r="P20" t="n">
-        <v>27.20673720636894</v>
+        <v>26.65662127108736</v>
       </c>
       <c r="Q20" t="n">
-        <v>269298.803786</v>
+        <v>273082.814069</v>
       </c>
       <c r="R20" t="n">
-        <v>0.712171906694686</v>
+        <v>0.707518966929726</v>
       </c>
       <c r="S20" t="n">
-        <v>206590.40261</v>
+        <v>210370.522951</v>
       </c>
       <c r="T20" t="n">
-        <v>0.546336927097911</v>
+        <v>0.545040285959372</v>
       </c>
       <c r="U20" t="n">
-        <v>62708.401176</v>
+        <v>62712.291118</v>
       </c>
       <c r="V20" t="n">
-        <v>0.165834979596775</v>
+        <v>0.162478680970354</v>
       </c>
       <c r="W20" t="n">
-        <v>3841879.008952</v>
+        <v>3849728.053465</v>
       </c>
       <c r="X20" t="n">
-        <v>10.16000910746666</v>
+        <v>9.974101170129764</v>
       </c>
     </row>
     <row r="21">

--- a/output/zone_monthly_4_01/renewable_electricity_generation_4_01.xlsx
+++ b/output/zone_monthly_4_01/renewable_electricity_generation_4_01.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1818,6 +1818,86 @@
       </c>
       <c r="X17" t="n">
         <v>10.24308447010312</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>05月</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3329172.244782</v>
+      </c>
+      <c r="E18" t="n">
+        <v>273694.199</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.221088573262511</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2242.804</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.06736821753561301</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1802039.58703</v>
+      </c>
+      <c r="J18" t="n">
+        <v>54.12875797743535</v>
+      </c>
+      <c r="K18" t="n">
+        <v>858830.2169999999</v>
+      </c>
+      <c r="L18" t="n">
+        <v>25.79710972738323</v>
+      </c>
+      <c r="M18" t="n">
+        <v>114193.949</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.430100355395628</v>
+      </c>
+      <c r="O18" t="n">
+        <v>744636.268</v>
+      </c>
+      <c r="P18" t="n">
+        <v>22.36700937198761</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>25254.442649</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.7585802353297501</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20762.026613</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.623639303900286</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4492.416036</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.134940931429463</v>
+      </c>
+      <c r="W18" t="n">
+        <v>367110.995103</v>
+      </c>
+      <c r="X18" t="n">
+        <v>11.02709526905356</v>
       </c>
     </row>
   </sheetData>

--- a/output/zone_monthly_4_01/renewable_electricity_generation_4_01.xlsx
+++ b/output/zone_monthly_4_01/renewable_electricity_generation_4_01.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1898,6 +1898,86 @@
       </c>
       <c r="X18" t="n">
         <v>11.02709526905356</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>06月</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3172369.37064</v>
+      </c>
+      <c r="E19" t="n">
+        <v>610997.728</v>
+      </c>
+      <c r="F19" t="n">
+        <v>19.25998068367229</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2408.652</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.075925963170993</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1533508.14627</v>
+      </c>
+      <c r="J19" t="n">
+        <v>48.33952062652235</v>
+      </c>
+      <c r="K19" t="n">
+        <v>667948.58</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21.05519572158922</v>
+      </c>
+      <c r="M19" t="n">
+        <v>72906.136</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.298160380526299</v>
+      </c>
+      <c r="O19" t="n">
+        <v>595042.444</v>
+      </c>
+      <c r="P19" t="n">
+        <v>18.75703534106292</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>21914.135077</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.690781321992748</v>
+      </c>
+      <c r="S19" t="n">
+        <v>17538.989587</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.552867196024581</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4375.14549</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.137914125968167</v>
+      </c>
+      <c r="W19" t="n">
+        <v>335592.129293</v>
+      </c>
+      <c r="X19" t="n">
+        <v>10.57859568305241</v>
       </c>
     </row>
   </sheetData>
@@ -1911,7 +1991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2035,1564 +2115,6 @@
           <t>waste_share_pct</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>96年</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>8324811.934704</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4417549.905</v>
-      </c>
-      <c r="F2" t="n">
-        <v>53.06486128034161</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2180</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.02618677775665</v>
-      </c>
-      <c r="K2" t="n">
-        <v>439534.507</v>
-      </c>
-      <c r="L2" t="n">
-        <v>5.279813051003514</v>
-      </c>
-      <c r="M2" t="n">
-        <v>439534.507</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5.279813051003514</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>302267.46282</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3.630922418318241</v>
-      </c>
-      <c r="S2" t="n">
-        <v>246865.171468</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.96541439499531</v>
-      </c>
-      <c r="U2" t="n">
-        <v>55402.291352</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.665508023322931</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3163280.059884</v>
-      </c>
-      <c r="X2" t="n">
-        <v>37.99821647257998</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>97年</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>8259059.525998</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4305105.175</v>
-      </c>
-      <c r="F3" t="n">
-        <v>52.1258523618618</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4473.143</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.054160440252542</v>
-      </c>
-      <c r="K3" t="n">
-        <v>588265.167</v>
-      </c>
-      <c r="L3" t="n">
-        <v>7.122665300428572</v>
-      </c>
-      <c r="M3" t="n">
-        <v>588265.167</v>
-      </c>
-      <c r="N3" t="n">
-        <v>7.122665300428572</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>272488.618017</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3.29926933156561</v>
-      </c>
-      <c r="S3" t="n">
-        <v>226997.261293</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.748463800005974</v>
-      </c>
-      <c r="U3" t="n">
-        <v>45491.356724</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.550805531559636</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3088727.422981</v>
-      </c>
-      <c r="X3" t="n">
-        <v>37.39805256589148</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>98年</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>7809525.084796</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3748288.19</v>
-      </c>
-      <c r="F4" t="n">
-        <v>47.99636532696933</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9112.535</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.116684880335947</v>
-      </c>
-      <c r="K4" t="n">
-        <v>786635.449</v>
-      </c>
-      <c r="L4" t="n">
-        <v>10.07276934843918</v>
-      </c>
-      <c r="M4" t="n">
-        <v>786635.449</v>
-      </c>
-      <c r="N4" t="n">
-        <v>10.07276934843918</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>229349.505573</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.936791969840904</v>
-      </c>
-      <c r="S4" t="n">
-        <v>187520.859995</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.401181351732586</v>
-      </c>
-      <c r="U4" t="n">
-        <v>41828.645578</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.535610618108318</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3036139.405223</v>
-      </c>
-      <c r="X4" t="n">
-        <v>38.87738847441463</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>99年</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>8639758.042541999</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4194101.306</v>
-      </c>
-      <c r="F5" t="n">
-        <v>48.544198637836</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>21727.004</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.251476996149853</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1026337.795</v>
-      </c>
-      <c r="L5" t="n">
-        <v>11.87924233463868</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1026337.795</v>
-      </c>
-      <c r="N5" t="n">
-        <v>11.87924233463868</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>270037.645284</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.125523237506651</v>
-      </c>
-      <c r="S5" t="n">
-        <v>234679.030936</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.71626855498088</v>
-      </c>
-      <c r="U5" t="n">
-        <v>35358.614348</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.409254682525771</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3127554.292258</v>
-      </c>
-      <c r="X5" t="n">
-        <v>36.1995587938688</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100年</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>8987061.019835999</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3999726.499</v>
-      </c>
-      <c r="F6" t="n">
-        <v>44.50538936112608</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>61622.537</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.685680634236136</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1492676.671</v>
-      </c>
-      <c r="L6" t="n">
-        <v>16.60917476475796</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1492676.671</v>
-      </c>
-      <c r="N6" t="n">
-        <v>16.60917476475796</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>236091.087292</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.62701106369375</v>
-      </c>
-      <c r="S6" t="n">
-        <v>209738.96334</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.333788130258266</v>
-      </c>
-      <c r="U6" t="n">
-        <v>26352.123952</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.293222933435484</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3196944.225544</v>
-      </c>
-      <c r="X6" t="n">
-        <v>35.57274417618608</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>101年</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10662707.709069</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5669557.962</v>
-      </c>
-      <c r="F7" t="n">
-        <v>53.17184074339622</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>159869.831</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.499336147646861</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1413468.482</v>
-      </c>
-      <c r="L7" t="n">
-        <v>13.25618708274069</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1413468.482</v>
-      </c>
-      <c r="N7" t="n">
-        <v>13.25618708274069</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>242070.124744</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.270250027937191</v>
-      </c>
-      <c r="S7" t="n">
-        <v>218577.389997</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.049923865127546</v>
-      </c>
-      <c r="U7" t="n">
-        <v>23492.734747</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.220326162809646</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3177741.309325</v>
-      </c>
-      <c r="X7" t="n">
-        <v>29.80238599827905</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>102年</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10858145.914143</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5422889.721</v>
-      </c>
-      <c r="F8" t="n">
-        <v>49.94305440246989</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>321096.236</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.957192125975801</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1640007.611</v>
-      </c>
-      <c r="L8" t="n">
-        <v>15.10393785428735</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1640007.611</v>
-      </c>
-      <c r="N8" t="n">
-        <v>15.10393785428735</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>228480.693489</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.104233036612616</v>
-      </c>
-      <c r="S8" t="n">
-        <v>205349.845969</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.891205437767481</v>
-      </c>
-      <c r="U8" t="n">
-        <v>23130.84752</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.213027598845135</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3245671.652654</v>
-      </c>
-      <c r="X8" t="n">
-        <v>29.89158258065434</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>103年</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>9925065.711755</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4317861.918</v>
-      </c>
-      <c r="F9" t="n">
-        <v>43.50461793805589</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>528762.129</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.327542853179776</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1500484.383</v>
-      </c>
-      <c r="L9" t="n">
-        <v>15.11813046459596</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1500484.383</v>
-      </c>
-      <c r="N9" t="n">
-        <v>15.11813046459596</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>252466.961581</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.543730882123878</v>
-      </c>
-      <c r="S9" t="n">
-        <v>231913.426565</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.336643739197893</v>
-      </c>
-      <c r="U9" t="n">
-        <v>20553.535016</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.207087142925985</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3325490.320174</v>
-      </c>
-      <c r="X9" t="n">
-        <v>33.50597786204451</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>104年</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10478832.561957</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4470146.125</v>
-      </c>
-      <c r="F10" t="n">
-        <v>42.65881813236233</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>850267.948</v>
-      </c>
-      <c r="J10" t="n">
-        <v>8.11414766838498</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1525235.707</v>
-      </c>
-      <c r="L10" t="n">
-        <v>14.55539725424481</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1525235.707</v>
-      </c>
-      <c r="N10" t="n">
-        <v>14.55539725424481</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>248990.698738</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.376130139171716</v>
-      </c>
-      <c r="S10" t="n">
-        <v>227420.045409</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.170280363431321</v>
-      </c>
-      <c r="U10" t="n">
-        <v>21570.653329</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.205849775740395</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3384192.083219</v>
-      </c>
-      <c r="X10" t="n">
-        <v>32.29550680583618</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>105年</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12732754.835034</v>
-      </c>
-      <c r="E11" t="n">
-        <v>6562040.858</v>
-      </c>
-      <c r="F11" t="n">
-        <v>51.53669369290481</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1109004.65</v>
-      </c>
-      <c r="J11" t="n">
-        <v>8.709856306575455</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1457101.846</v>
-      </c>
-      <c r="L11" t="n">
-        <v>11.4437281238684</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1457101.846</v>
-      </c>
-      <c r="N11" t="n">
-        <v>11.4437281238684</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>208055.709783</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.634019601245581</v>
-      </c>
-      <c r="S11" t="n">
-        <v>185761.624023</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.458927203340784</v>
-      </c>
-      <c r="U11" t="n">
-        <v>22294.08576</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.175092397904797</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3396551.771251</v>
-      </c>
-      <c r="X11" t="n">
-        <v>26.67570227540575</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>106年</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12369312.430806</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5446814.787</v>
-      </c>
-      <c r="F12" t="n">
-        <v>44.03490345538211</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1667452.949</v>
-      </c>
-      <c r="J12" t="n">
-        <v>13.4805629522881</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1722458.624</v>
-      </c>
-      <c r="L12" t="n">
-        <v>13.92525763768555</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1702077.483</v>
-      </c>
-      <c r="N12" t="n">
-        <v>13.76048581941341</v>
-      </c>
-      <c r="O12" t="n">
-        <v>20381.141</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.164771818272133</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>191585.375949</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.548876520184365</v>
-      </c>
-      <c r="S12" t="n">
-        <v>169449.983664</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.369922415751919</v>
-      </c>
-      <c r="U12" t="n">
-        <v>22135.392285</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.178954104432445</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3341000.694857</v>
-      </c>
-      <c r="X12" t="n">
-        <v>27.01039943445989</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>107年</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12610980.98976</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4481644.615</v>
-      </c>
-      <c r="F13" t="n">
-        <v>35.53763675196287</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.473</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.1680296729e-05</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2661601.42031</v>
-      </c>
-      <c r="J13" t="n">
-        <v>21.10542726589784</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1709487.194</v>
-      </c>
-      <c r="L13" t="n">
-        <v>13.55554492856732</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1682777.103</v>
-      </c>
-      <c r="N13" t="n">
-        <v>13.34374466479967</v>
-      </c>
-      <c r="O13" t="n">
-        <v>26710.091</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.211800263767651</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>191649.314773</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.519701876710602</v>
-      </c>
-      <c r="S13" t="n">
-        <v>166439.859696</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.319801051410256</v>
-      </c>
-      <c r="U13" t="n">
-        <v>25209.455077</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.199900825300346</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3566596.972677</v>
-      </c>
-      <c r="X13" t="n">
-        <v>28.28167749656465</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>108年</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>15213822.711301</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5544795.913</v>
-      </c>
-      <c r="F14" t="n">
-        <v>36.44577709507067</v>
-      </c>
-      <c r="G14" t="n">
-        <v>756.7089999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.004973825542465</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3964656.3578</v>
-      </c>
-      <c r="J14" t="n">
-        <v>26.05956723062777</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1892231.711</v>
-      </c>
-      <c r="L14" t="n">
-        <v>12.43758223628062</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1715854.79</v>
-      </c>
-      <c r="N14" t="n">
-        <v>11.27826202894716</v>
-      </c>
-      <c r="O14" t="n">
-        <v>176376.921</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.159320207333462</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>176520.875277</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.160266414475031</v>
-      </c>
-      <c r="S14" t="n">
-        <v>151433.827166</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.99537000029265</v>
-      </c>
-      <c r="U14" t="n">
-        <v>25087.048111</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.164896414182381</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3634861.145224</v>
-      </c>
-      <c r="X14" t="n">
-        <v>23.89183319800344</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>109年</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>15358826.973947</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3019152.286</v>
-      </c>
-      <c r="F15" t="n">
-        <v>19.65744057877176</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1911.729</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.012447102915104</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6247392.93088</v>
-      </c>
-      <c r="J15" t="n">
-        <v>40.67623745926289</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2308871.786</v>
-      </c>
-      <c r="L15" t="n">
-        <v>15.03286539991962</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1792791.113</v>
-      </c>
-      <c r="N15" t="n">
-        <v>11.67270857365013</v>
-      </c>
-      <c r="O15" t="n">
-        <v>516080.673</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.36015682626949</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>211753.876417</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.378711256896087</v>
-      </c>
-      <c r="S15" t="n">
-        <v>141365.508753</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.920418655622572</v>
-      </c>
-      <c r="U15" t="n">
-        <v>70388.367664</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.458292601273515</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3569744.36565</v>
-      </c>
-      <c r="X15" t="n">
-        <v>23.24229820223456</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>110年</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>17911702.572427</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3474662.53497</v>
-      </c>
-      <c r="F16" t="n">
-        <v>19.39884006514736</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9073.845009999999</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.050658752138773</v>
-      </c>
-      <c r="I16" t="n">
-        <v>8350960.95629</v>
-      </c>
-      <c r="J16" t="n">
-        <v>46.62293225628557</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2270783.86033</v>
-      </c>
-      <c r="L16" t="n">
-        <v>12.67765501993992</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1701479.84833</v>
-      </c>
-      <c r="N16" t="n">
-        <v>9.499263631974506</v>
-      </c>
-      <c r="O16" t="n">
-        <v>569304.012</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.178391387965418</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>201707.476824</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.12612118255305</v>
-      </c>
-      <c r="S16" t="n">
-        <v>153172.266681</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.8551519101081489</v>
-      </c>
-      <c r="U16" t="n">
-        <v>48535.210143</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.270969272444901</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3604513.899003</v>
-      </c>
-      <c r="X16" t="n">
-        <v>20.12379272393532</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>111年</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>24110836.364907</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5836502.66401</v>
-      </c>
-      <c r="F17" t="n">
-        <v>24.20696891504333</v>
-      </c>
-      <c r="G17" t="n">
-        <v>25007.71</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.103719794790688</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10898818.42392</v>
-      </c>
-      <c r="J17" t="n">
-        <v>45.20298781415598</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3577472.27299</v>
-      </c>
-      <c r="L17" t="n">
-        <v>14.83761168151331</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2082793.93799</v>
-      </c>
-      <c r="N17" t="n">
-        <v>8.638414306612271</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1494678.335</v>
-      </c>
-      <c r="P17" t="n">
-        <v>6.199197374901039</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>164213.814059</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.681078879113505</v>
-      </c>
-      <c r="S17" t="n">
-        <v>118196.010273</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.490219453544269</v>
-      </c>
-      <c r="U17" t="n">
-        <v>46017.803786</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.190859425569236</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3608821.479928</v>
-      </c>
-      <c r="X17" t="n">
-        <v>14.96763291538319</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>112年</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>27432092.099754</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3963919.556</v>
-      </c>
-      <c r="F18" t="n">
-        <v>14.44993528596219</v>
-      </c>
-      <c r="G18" t="n">
-        <v>23164.354</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.084442535100003</v>
-      </c>
-      <c r="I18" t="n">
-        <v>13340351.2854</v>
-      </c>
-      <c r="J18" t="n">
-        <v>48.63045529626095</v>
-      </c>
-      <c r="K18" t="n">
-        <v>6238286.52899</v>
-      </c>
-      <c r="L18" t="n">
-        <v>22.74083400677247</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1741013.43299</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.346630168267818</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4497273.096</v>
-      </c>
-      <c r="P18" t="n">
-        <v>16.39420383850465</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>244040.018872</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.889615046437484</v>
-      </c>
-      <c r="S18" t="n">
-        <v>171197.552736</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.62407763911501</v>
-      </c>
-      <c r="U18" t="n">
-        <v>72842.466136</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.265537407322474</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3622330.356492</v>
-      </c>
-      <c r="X18" t="n">
-        <v>13.20471782946691</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>113年</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>34129160.722314</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4210637.67799</v>
-      </c>
-      <c r="F19" t="n">
-        <v>12.33736074628123</v>
-      </c>
-      <c r="G19" t="n">
-        <v>26740.734</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.078351572186528</v>
-      </c>
-      <c r="I19" t="n">
-        <v>15498625.38828</v>
-      </c>
-      <c r="J19" t="n">
-        <v>45.41168039373098</v>
-      </c>
-      <c r="K19" t="n">
-        <v>10509811.45099</v>
-      </c>
-      <c r="L19" t="n">
-        <v>30.79422765916004</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1898368.85098</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5.562307454395814</v>
-      </c>
-      <c r="O19" t="n">
-        <v>8611442.60001</v>
-      </c>
-      <c r="P19" t="n">
-        <v>25.23192020476422</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>237409.188782</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.695619768425127</v>
-      </c>
-      <c r="S19" t="n">
-        <v>173462.86305</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.5082541128431211</v>
-      </c>
-      <c r="U19" t="n">
-        <v>63946.325732</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.187365655582006</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3645936.282272</v>
-      </c>
-      <c r="X19" t="n">
-        <v>10.6827598602161</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>114年</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>38597242.877324</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5506148.836</v>
-      </c>
-      <c r="F20" t="n">
-        <v>14.26565325792967</v>
-      </c>
-      <c r="G20" t="n">
-        <v>25842.798</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.06695503635360101</v>
-      </c>
-      <c r="I20" t="n">
-        <v>16739152.66588</v>
-      </c>
-      <c r="J20" t="n">
-        <v>43.36877822875349</v>
-      </c>
-      <c r="K20" t="n">
-        <v>12203287.70991</v>
-      </c>
-      <c r="L20" t="n">
-        <v>31.61699333990374</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1914566.85502</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.960372068816382</v>
-      </c>
-      <c r="O20" t="n">
-        <v>10288720.85489</v>
-      </c>
-      <c r="P20" t="n">
-        <v>26.65662127108736</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>273082.814069</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.707518966929726</v>
-      </c>
-      <c r="S20" t="n">
-        <v>210370.522951</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.545040285959372</v>
-      </c>
-      <c r="U20" t="n">
-        <v>62712.291118</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.162478680970354</v>
-      </c>
-      <c r="W20" t="n">
-        <v>3849728.053465</v>
-      </c>
-      <c r="X20" t="n">
-        <v>9.974101170129764</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>115年</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
